--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.74376766634612</v>
+        <v>5.320862245781245</v>
       </c>
       <c r="D2" t="n">
-        <v>21.99147562124925</v>
+        <v>3.573614788453003</v>
       </c>
       <c r="E2" t="n">
-        <v>10.97907578743607</v>
+        <v>1.784099815458362</v>
       </c>
       <c r="F2" t="n">
-        <v>26.77123998062404</v>
+        <v>4.350326496851407</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.28459058868476</v>
+        <v>6.221245970661274</v>
       </c>
       <c r="D3" t="n">
-        <v>66.3974773617191</v>
+        <v>10.78959007127935</v>
       </c>
       <c r="E3" t="n">
-        <v>10.97907578743607</v>
+        <v>1.784099815458362</v>
       </c>
       <c r="F3" t="n">
-        <v>26.77123998062404</v>
+        <v>4.350326496851407</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.8366026888506</v>
+        <v>10.04844793693822</v>
       </c>
       <c r="D4" t="n">
-        <v>96.5226657319409</v>
+        <v>15.6849331814404</v>
       </c>
       <c r="E4" t="n">
-        <v>10.97907578743607</v>
+        <v>1.784099815458362</v>
       </c>
       <c r="F4" t="n">
-        <v>26.77123998062404</v>
+        <v>4.350326496851407</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.73313217322244</v>
+        <v>6.781633978148648</v>
       </c>
       <c r="D5" t="n">
-        <v>70.22849942695083</v>
+        <v>11.41213115687951</v>
       </c>
       <c r="E5" t="n">
-        <v>10.97907578743607</v>
+        <v>1.784099815458362</v>
       </c>
       <c r="F5" t="n">
-        <v>26.77123998062404</v>
+        <v>4.350326496851407</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
